--- a/ProyectoSoftwareSistemas/bin/Debug/output/bloq2_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/bloq2_ArchivoIntermedio.xlsx
@@ -9,6 +9,7 @@
     <x:sheet name="ArchivoIntermedio" sheetId="1" r:id="rId2"/>
     <x:sheet name="ProgramaObjeto" sheetId="2" r:id="rId3"/>
     <x:sheet name="TABBLK" sheetId="3" r:id="rId4"/>
+    <x:sheet name="TABSIM" sheetId="4" r:id="rId5"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -126,7 +127,7 @@
     <x:t>Indexado</x:t>
   </x:si>
   <x:si>
-    <x:t>17AFD7</x:t>
+    <x:t>17A041</x:t>
   </x:si>
   <x:si>
     <x:t>0029</x:t>
@@ -219,7 +220,7 @@
     <x:t>(NUM+TABLA-CTE)*10</x:t>
   </x:si>
   <x:si>
-    <x:t>00008C</x:t>
+    <x:t>FFFE7A</x:t>
   </x:si>
   <x:si>
     <x:t>002C</x:t>
@@ -294,7 +295,7 @@
     <x:t>CTE,X</x:t>
   </x:si>
   <x:si>
-    <x:t>23AFFC</x:t>
+    <x:t>23A066</x:t>
   </x:si>
   <x:si>
     <x:t>0006</x:t>
@@ -318,7 +319,7 @@
     <x:t>SALTO,X</x:t>
   </x:si>
   <x:si>
-    <x:t>3FAFF6</x:t>
+    <x:t>3FA14E</x:t>
   </x:si>
   <x:si>
     <x:t>000D</x:t>
@@ -369,7 +370,7 @@
     <x:t>NUM,X</x:t>
   </x:si>
   <x:si>
-    <x:t>0390000E*</x:t>
+    <x:t>03900043*</x:t>
   </x:si>
   <x:si>
     <x:t>0035</x:t>
@@ -384,13 +385,13 @@
     <x:t>HEJERFI000000000035</x:t>
   </x:si>
   <x:si>
-    <x:t>T0000260B17AFD7038110003400007D</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T0000641C4E4F4D42524500008C297FFFFF6FEFFFB450FFFFFF23AFFC757FFFFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00000A113FAFF60FFFFFFFFFFFFF29000E0390000E</x:t>
+    <x:t>T0000260B17A041038110003400007D</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T0000641C4E4F4D425245FFFE7A297FFFFF6FEFFFB450FFFFFF23A066757FFFFF</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00000A113FA14E0FFFFFFFFFFFFF29000E03900043</x:t>
   </x:si>
   <x:si>
     <x:t>M00007405+EJERFI</x:t>
@@ -421,6 +422,39 @@
   </x:si>
   <x:si>
     <x:t>00AC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Simbolo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Direccion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tipo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Relativo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bloque</x:t>
+  </x:si>
+  <x:si>
+    <x:t>R</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sí</x:t>
+  </x:si>
+  <x:si>
+    <x:t>000E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FFFF</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1815,7 +1849,7 @@
   <x:dimension ref="A1:A6"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="70.710625" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="70.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
@@ -1933,4 +1967,249 @@
   <x:headerFooter/>
   <x:tableParts count="0"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:E13"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8.282054" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="9.139196" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="4.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.139196" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="8.853482" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:5">
+      <x:c r="A1" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B1" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C1" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="D1" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="E1" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:5">
+      <x:c r="A2" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:5">
+      <x:c r="A3" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:5">
+      <x:c r="A4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="A5" s="0" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="A6" s="0" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5">
+      <x:c r="A7" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
+      <x:c r="A8" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:5">
+      <x:c r="A9" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:5">
+      <x:c r="A10" s="0" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:5">
+      <x:c r="A11" s="0" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="B11" s="0" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:5">
+      <x:c r="A12" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B12" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:5">
+      <x:c r="A13" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
 </file>
--- a/ProyectoSoftwareSistemas/bin/Debug/output/bloq2_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/bloq2_ArchivoIntermedio.xlsx
@@ -85,7 +85,7 @@
     <x:t>--</x:t>
   </x:si>
   <x:si>
-    <x:t>Error: Registro inválido en segundo operando</x:t>
+    <x:t>A449</x:t>
   </x:si>
   <x:si>
     <x:t>0002</x:t>
@@ -127,7 +127,7 @@
     <x:t>Indexado</x:t>
   </x:si>
   <x:si>
-    <x:t>17A041</x:t>
+    <x:t>17A00C</x:t>
   </x:si>
   <x:si>
     <x:t>0029</x:t>
@@ -238,10 +238,7 @@
     <x:t>Inmediato</x:t>
   </x:si>
   <x:si>
-    <x:t>Símbolo no encontrado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>297FFFFF</x:t>
+    <x:t>2910003A*</x:t>
   </x:si>
   <x:si>
     <x:t>0030</x:t>
@@ -295,7 +292,7 @@
     <x:t>CTE,X</x:t>
   </x:si>
   <x:si>
-    <x:t>23A066</x:t>
+    <x:t>23AF85</x:t>
   </x:si>
   <x:si>
     <x:t>0006</x:t>
@@ -307,7 +304,10 @@
     <x:t>#NUM-SALTO</x:t>
   </x:si>
   <x:si>
-    <x:t>757FFFFF</x:t>
+    <x:t>Expresión no válida como dirección</x:t>
+  </x:si>
+  <x:si>
+    <x:t>753FFFFF</x:t>
   </x:si>
   <x:si>
     <x:t>000A</x:t>
@@ -319,7 +319,7 @@
     <x:t>SALTO,X</x:t>
   </x:si>
   <x:si>
-    <x:t>3FA14E</x:t>
+    <x:t>3FAFF6</x:t>
   </x:si>
   <x:si>
     <x:t>000D</x:t>
@@ -328,19 +328,22 @@
     <x:t>+STA</x:t>
   </x:si>
   <x:si>
-    <x:t>-SALTO+NUM-(-VALOR-CONT),X</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Error: Símbolo duplicado | Símbolo no encontrado</x:t>
-  </x:si>
-  <x:si>
-    <x:t>0FFFFFFF</x:t>
+    <x:t>-SALTO+NUM+(VALOR-CONT),X</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Error: Símbolo duplicado</x:t>
+  </x:si>
+  <x:si>
+    <x:t>0F90003E*</x:t>
   </x:si>
   <x:si>
     <x:t>006D</x:t>
   </x:si>
   <x:si>
-    <x:t>((SALTO-CTE)-(-EXPR2))+15</x:t>
+    <x:t>((SALTO-CTE)+(EXPR2))+15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>000126*</x:t>
   </x:si>
   <x:si>
     <x:t>0070</x:t>
@@ -361,7 +364,7 @@
     <x:t>CALC</x:t>
   </x:si>
   <x:si>
-    <x:t>Error: Símbolos de diferentes bloques en EQU | Error: Símbolos de diferentes bloques en EQU | Expresión relativa inválida</x:t>
+    <x:t xml:space="preserve">Error: Símbolos de diferentes bloques en EQU | Error: Símbolos de diferentes bloques en EQU | </x:t>
   </x:si>
   <x:si>
     <x:t>+LDA</x:t>
@@ -370,7 +373,7 @@
     <x:t>NUM,X</x:t>
   </x:si>
   <x:si>
-    <x:t>03900043*</x:t>
+    <x:t>0390000E</x:t>
   </x:si>
   <x:si>
     <x:t>0035</x:t>
@@ -382,22 +385,43 @@
     <x:t>FIRST</x:t>
   </x:si>
   <x:si>
-    <x:t>HEJERFI000000000035</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T0000260B17A041038110003400007D</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T0000641C4E4F4D425245FFFE7A297FFFFF6FEFFFB450FFFFFF23A066757FFFFF</x:t>
-  </x:si>
-  <x:si>
-    <x:t>T00000A113FA14E0FFFFFFFFFFFFF29000E03900043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>M00007405+EJERFI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>E000000</x:t>
+    <x:t>Símbolo no definido: FIRST</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HEJERFI0000000000BD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00000002A449</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T0000260617A00C038110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00003505003400007D</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T000099094E4F4D425245FFFE7A</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T00002C092910003A6FEFFFB450</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T0000AC11FFFFFF23AF85753FFFFF3FAFF60F90003E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>T0000A20A00012629000E0390000E</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M00002D05+EJERFI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M0000BA05+EJERFI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M0000A206+EJERFI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EFFFFFF</x:t>
   </x:si>
   <x:si>
     <x:t>No. Bloque</x:t>
@@ -898,10 +922,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J3" s="0" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="J3" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:10">
@@ -1378,10 +1402,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J18" s="0" t="s">
         <x:v>73</x:v>
-      </x:c>
-      <x:c r="J18" s="0" t="s">
-        <x:v>74</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
@@ -1392,16 +1416,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D19" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E19" s="0" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="D19" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E19" s="0" t="s">
+      <x:c r="F19" s="0" t="s">
         <x:v>76</x:v>
-      </x:c>
-      <x:c r="F19" s="0" t="s">
-        <x:v>77</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
         <x:v>34</x:v>
@@ -1410,10 +1434,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="I19" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="J19" s="0" t="s">
         <x:v>78</x:v>
-      </x:c>
-      <x:c r="J19" s="0" t="s">
-        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
@@ -1424,16 +1448,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D20" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="0" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="D20" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E20" s="0" t="s">
+      <x:c r="F20" s="0" t="s">
         <x:v>81</x:v>
-      </x:c>
-      <x:c r="F20" s="0" t="s">
-        <x:v>82</x:v>
       </x:c>
       <x:c r="G20" s="0" t="s">
         <x:v>20</x:v>
@@ -1445,7 +1469,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J20" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
@@ -1465,7 +1489,7 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
         <x:v>14</x:v>
@@ -1497,7 +1521,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
         <x:v>14</x:v>
@@ -1506,10 +1530,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="J22" s="0" t="s">
         <x:v>86</x:v>
-      </x:c>
-      <x:c r="J22" s="0" t="s">
-        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
@@ -1520,16 +1544,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D23" s="0" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D23" s="0" t="s">
+      <x:c r="E23" s="0" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="E23" s="0" t="s">
+      <x:c r="F23" s="0" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="F23" s="0" t="s">
-        <x:v>91</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
         <x:v>34</x:v>
@@ -1541,7 +1565,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
@@ -1552,16 +1576,16 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D24" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E24" s="0" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
+      <x:c r="F24" s="0" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>95</x:v>
       </x:c>
       <x:c r="G24" s="0" t="s">
         <x:v>71</x:v>
@@ -1570,7 +1594,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="J24" s="0" t="s">
         <x:v>96</x:v>
@@ -1698,10 +1722,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I28" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="J28" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
@@ -1712,16 +1736,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
         <x:v>34</x:v>
@@ -1733,7 +1757,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10">
@@ -1744,10 +1768,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
         <x:v>29</x:v>
@@ -1762,7 +1786,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
         <x:v>17</x:v>
@@ -1776,16 +1800,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
         <x:v>71</x:v>
@@ -1797,7 +1821,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="J31" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
@@ -1808,16 +1832,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
         <x:v>14</x:v>
@@ -1826,7 +1850,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
         <x:v>17</x:v>
@@ -1846,40 +1870,70 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:A6"/>
+  <x:dimension ref="A1:A12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="70.567768" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="46.853482" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:1">
       <x:c r="A1" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:1">
       <x:c r="A2" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:1">
       <x:c r="A3" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:1">
       <x:c r="A4" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:1">
       <x:c r="A5" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:1">
       <x:c r="A6" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:1">
+      <x:c r="A7" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:1">
+      <x:c r="A8" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:1">
+      <x:c r="A9" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:1">
+      <x:c r="A10" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:1">
+      <x:c r="A11" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:1">
+      <x:c r="A12" s="0" t="s">
+        <x:v>134</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1906,16 +1960,16 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
@@ -1923,10 +1977,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>10</x:v>
@@ -1940,10 +1994,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
@@ -1951,13 +2005,13 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1986,19 +2040,19 @@
   <x:sheetData>
     <x:row r="1" spans="1:5">
       <x:c r="A1" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B1" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C1" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D1" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E1" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>147</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:5">
@@ -2009,13 +2063,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
@@ -2026,13 +2080,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
@@ -2043,13 +2097,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
@@ -2057,13 +2111,13 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
         <x:v>42</x:v>
@@ -2077,10 +2131,10 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
         <x:v>42</x:v>
@@ -2094,10 +2148,10 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
         <x:v>42</x:v>
@@ -2111,10 +2165,10 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>42</x:v>
@@ -2128,10 +2182,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
         <x:v>42</x:v>
@@ -2142,13 +2196,13 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>42</x:v>
@@ -2162,10 +2216,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
         <x:v>42</x:v>
@@ -2173,33 +2227,33 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>42</x:v>

--- a/ProyectoSoftwareSistemas/bin/Debug/output/bloq2_ArchivoIntermedio.xlsx
+++ b/ProyectoSoftwareSistemas/bin/Debug/output/bloq2_ArchivoIntermedio.xlsx
@@ -8,8 +8,8 @@
   <x:sheets>
     <x:sheet name="ArchivoIntermedio" sheetId="1" r:id="rId2"/>
     <x:sheet name="ProgramaObjeto" sheetId="2" r:id="rId3"/>
-    <x:sheet name="TABBLK" sheetId="3" r:id="rId4"/>
-    <x:sheet name="TABSIM" sheetId="4" r:id="rId5"/>
+    <x:sheet name="TABBLK_DEFAULT" sheetId="3" r:id="rId4"/>
+    <x:sheet name="TABSIM_DEFAULT" sheetId="4" r:id="rId5"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -385,7 +385,7 @@
     <x:t>FIRST</x:t>
   </x:si>
   <x:si>
-    <x:t>Símbolo no definido: FIRST</x:t>
+    <x:t>Error: símbolo de END no pertenece a la sección principal | Símbolo no definido: FIRST</x:t>
   </x:si>
   <x:si>
     <x:t>HEJERFI0000000000BD</x:t>
@@ -831,6 +831,18 @@
   </x:sheetPr>
   <x:dimension ref="A1:J32"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="5.282054" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.996339" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.853482" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="28.853482" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="9.710625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="10.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="86.710625" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.853482" style="0" customWidth="1"/>
+  </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:10">
       <x:c r="A1" s="0" t="s">
